--- a/public/templates/forms/A-005-RACIMatrixForCybersecurity-FORM.xlsx
+++ b/public/templates/forms/A-005-RACIMatrixForCybersecurity-FORM.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="20160" windowHeight="20280" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="20160" windowHeight="20280" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="1" state="visible" r:id="rId1"/>
@@ -621,7 +621,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="50.5" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Classification</t>
@@ -640,7 +640,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="34.7" customHeight="1">
       <c r="A9" s="22" t="inlineStr">
         <is>
           <t>This matrix maps each major cybersecurity function to the roles that carry it, so every duty has a clear owner. It shows who is Responsible, Accountable, Consulted, and Informed for the work defined across the Agency’s other security artifacts.</t>
@@ -654,14 +654,14 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="22" t="inlineStr">
         <is>
           <t>Each row is a security function; each column is a role group. Each cell shows that role’s involvement using RACI: R = Responsible (does the work); A = Accountable (owns the outcome, one per row); C = Consulted (gives input); I = Informed (kept up to date).</t>
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="22" t="inlineStr">
         <is>
           <t>At a small Agency one person may hold several roles; where that happens, the same person carries those letters. Adjust the cells to match the Agency’s actual structure. The role columns map to the Security Role Descriptions.</t>
@@ -675,14 +675,14 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="34.7" customHeight="1">
       <c r="A16" s="23" t="inlineStr">
         <is>
           <t>« The cells below carry a suggested starting assignment. Review every row and adjust to the Agency’s structure. Keep exactly one A per row. »</t>
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="50.5" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Security Function \ Role</t>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="50.5" customHeight="1">
       <c r="A34" s="22" t="inlineStr">
         <is>
           <t>Where a function is contracted out, the vendor or county IT carries the Responsible role and the Agency keeps the Accountable role. Confirm assignments against the Security Role Descriptions and the IT Support Accountability Agreement. [Add Agency-specific exceptions.]</t>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="34.7" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
         <is>
           <t>Version</t>
@@ -1364,8 +1364,34 @@
     <mergeCell ref="A33:G33"/>
     <mergeCell ref="C3:G3"/>
   </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <dataValidations count="6">
+    <dataValidation sqref="B18:B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Director / Coordinator" prompt="Select a value" type="list">
+      <formula1>"R,A,C,I"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation sqref="C18:C31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Cybersecurity &amp; Privacy Lead" prompt="Select a value" type="list">
+      <formula1>"R,A,C,I"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation sqref="D18:D31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="County / Contracted IT" prompt="Select a value" type="list">
+      <formula1>"R,A,C,I"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation sqref="E18:E31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Dispatch Supervisor" prompt="Select a value" type="list">
+      <formula1>"R,A,C,I"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation sqref="F18:F31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Vendor / Service Provider" prompt="Select a value" type="list">
+      <formula1>"R,A,C,I"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation sqref="G18:G31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="All Personnel" prompt="Select a value" type="list">
+      <formula1>"R,A,C,I"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1373,7 +1399,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1409,14 +1435,14 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="34.7" customHeight="1">
       <c r="A6" s="22" t="inlineStr">
         <is>
           <t>The grid ships with a suggested assignment. Adjust every row to the Agency’s structure and keep one A per row.</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="22" t="inlineStr">
         <is>
           <t>Where one person holds several roles (common at small agencies), that person carries the letters in each of those columns.</t>
@@ -1437,7 +1463,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="50.5" customHeight="1">
       <c r="A11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">PSAP Profile</t>
@@ -1449,7 +1475,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1">
+    <row r="12" ht="256.4" customHeight="1">
       <c r="A12" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">Small (1–5, no in-house IT)</t>
@@ -1461,7 +1487,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1">
+    <row r="13" ht="224.8" customHeight="1">
       <c r="A13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">Medium (6–25, shared county IT)</t>
@@ -1473,7 +1499,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="42" customHeight="1">
+    <row r="14" ht="367.3" customHeight="1">
       <c r="A14" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">Large (25+, dedicated IT/security)</t>
@@ -1494,6 +1520,7 @@
     <mergeCell ref="B13:B13"/>
     <mergeCell ref="B14:B14"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>